--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,112 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E8" s="3">
         <v>211800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>195600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>186600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>192900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>352100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>154700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>136600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>183300</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
       <c r="N8" s="3">
         <v>0</v>
       </c>
@@ -771,41 +774,44 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E9" s="3">
         <v>128800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>120600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>125100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>124700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>129100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>197300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>50800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>81700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>99800</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -815,41 +821,44 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>83500</v>
+      </c>
+      <c r="E10" s="3">
         <v>83000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>75000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>61500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>68200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>74900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>154800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>103900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>54900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>83500</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -859,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,41 +889,42 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E12" s="3">
         <v>18000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>38600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>88700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>14900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>11900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>39400</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1009,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1053,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1068,96 +1093,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>207400</v>
+      </c>
+      <c r="E17" s="3">
         <v>211600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>205900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>211600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>219600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>268100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>512700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>156900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>121800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>201700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-25000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-26700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-64100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-160600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-18400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,85 +1206,89 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-47300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-16900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-66900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-34700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-32800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-18800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7400</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-41900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-88400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-59200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-58000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-152900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-36900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1262,8 +1298,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1306,85 +1345,91 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-92000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-61400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-60900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-154000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-18000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-37200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-9200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>19500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7800</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1394,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1438,96 +1486,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-45900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-98600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-52200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-67000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-173600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-61000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-74800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-205700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-86500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1570,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1614,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1658,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1702,96 +1768,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E32" s="3">
         <v>47300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>16900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>66900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>34700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>32800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>18800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7400</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-61000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-74800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-205700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-86500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1834,101 +1909,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-61000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-74800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-205700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-86500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1945,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1963,52 +2048,56 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>186500</v>
+      </c>
+      <c r="E41" s="3">
         <v>252600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>304000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>289400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>309800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>327900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>415000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2051,40 +2140,43 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>82000</v>
+      </c>
+      <c r="E43" s="3">
         <v>71800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>70200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>61700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>60200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>54600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>39200</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2095,8 +2187,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2139,172 +2234,184 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E45" s="3">
         <v>53600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>47200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>49800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>56700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>800</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>303400</v>
+      </c>
+      <c r="E46" s="3">
         <v>378000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>421400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>399200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>419800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>439100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>472100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>1400</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>774900</v>
+      </c>
+      <c r="E47" s="3">
         <v>727300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>652400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>570600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>527600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>499900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>433000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>287500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E48" s="3">
         <v>95300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>94800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>93300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>92700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>94600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -2315,23 +2422,26 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E49" s="3">
         <v>14100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14300</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,8 +2457,8 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2359,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2403,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2447,16 +2563,19 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E52" s="3">
         <v>5500</v>
-      </c>
-      <c r="E52" s="3">
-        <v>4900</v>
       </c>
       <c r="F52" s="3">
         <v>4900</v>
@@ -2465,14 +2584,14 @@
         <v>4900</v>
       </c>
       <c r="H52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I52" s="3">
         <v>16000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2535,52 +2657,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1208400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1220200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1187100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1082400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1045100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1049600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>981700</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>288900</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2597,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2615,8 +2744,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2624,31 +2754,31 @@
         <v>1300</v>
       </c>
       <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -2659,40 +2789,43 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E58" s="3">
         <v>44200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>66100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>9000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>28000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2703,75 +2836,81 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E59" s="3">
         <v>36100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>64500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>77500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E60" s="3">
         <v>81600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>111700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>95700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>128000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>89000</v>
       </c>
       <c r="I60" s="3">
         <v>89000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="J60" s="3">
+        <v>89000</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2779,44 +2918,47 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>200</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>324000</v>
+      </c>
+      <c r="E61" s="3">
         <v>327400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>240500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>213400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>92800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>96300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2835,52 +2977,58 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E62" s="3">
         <v>65100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>56800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>58800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>79400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>51500</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>24600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2923,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2967,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3011,52 +3165,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>574400</v>
+      </c>
+      <c r="E66" s="3">
         <v>610000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>589700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>554400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>491600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>482400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>408900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>24800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3073,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3117,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3161,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3173,7 +3340,7 @@
         <v>74300</v>
       </c>
       <c r="F70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="G70" s="3">
         <v>0</v>
@@ -3205,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3249,52 +3419,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-542600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-528200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-506500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-475200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-414200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-380200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-305400</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>7300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3337,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3381,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3425,52 +3607,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>461700</v>
+        <v>559700</v>
       </c>
       <c r="E76" s="3">
+        <v>535900</v>
+      </c>
+      <c r="F76" s="3">
         <v>523200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>527900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>553500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>567200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>572800</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
         <v>264200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3513,101 +3701,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-61000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-74800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-205700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-86500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3624,41 +3821,42 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -3668,8 +3866,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3712,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3756,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3800,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3844,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3888,52 +4101,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E89" s="3">
         <v>16100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-23700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-12200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-25600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>9300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3950,38 +4169,39 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -3994,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4038,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4082,52 +4308,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-125200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-91200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-99700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-73600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-87800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-104000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>48500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-190700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-287500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4144,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4188,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4232,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4276,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4320,61 +4562,67 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E100" s="3">
         <v>63400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>110300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>103000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>46000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>37100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>354900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>20900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>243900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>289000</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4390,8 +4638,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4408,48 +4656,54 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-47200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>14600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-62900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>225200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>85300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>51000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>62500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -656,118 +656,122 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E8" s="3">
         <v>218000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>211800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>195600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>186600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>192900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>352100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>154700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>136600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>183300</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
@@ -777,44 +781,47 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>144900</v>
+      </c>
+      <c r="E9" s="3">
         <v>134500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>128800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>120600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>125100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>124700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>129100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>197300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>50800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>81700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>99800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -824,44 +831,47 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100400</v>
+      </c>
+      <c r="E10" s="3">
         <v>83500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>75000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>61500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>68200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>74900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>154800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>103900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>54900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>83500</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,44 +903,45 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E12" s="3">
         <v>17600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>88700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>14900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>11900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>39400</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,8 +1001,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1031,8 +1051,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1078,8 +1101,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,102 +1120,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>237600</v>
+      </c>
+      <c r="E17" s="3">
         <v>207400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>211600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>205900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>211600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>219600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>268100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>512700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>156900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>121800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>201700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>100</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E18" s="3">
         <v>10600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-25000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-26700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-64100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-160600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-18400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,91 +1240,95 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-25600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-47300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-66900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-34700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-18800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-41900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-88400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-59200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-58000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-152900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-36900</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1301,8 +1338,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1348,91 +1388,97 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-15000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-47100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-92000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-61400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-60900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-154000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-37200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>19500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7800</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-20000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-45900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-98600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-52200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-67000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-173600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-45000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-61000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-74800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-205700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-86500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,102 +1838,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E32" s="3">
         <v>25600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>47300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>66900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>34700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>18800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-61000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-74800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-205700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-86500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-61000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-74800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-205700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-86500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,55 +2135,59 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E41" s="3">
         <v>186500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>252600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>304000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>289400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>309800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>327900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>415000</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3">
         <v>700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2143,43 +2233,46 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E43" s="3">
         <v>82000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>71800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>70200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>61700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>60200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>54600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>39200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3">
-        <v>0</v>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -2190,8 +2283,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2237,184 +2333,196 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E45" s="3">
         <v>34900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>53600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>47200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>48100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>56700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>17900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>399100</v>
+      </c>
+      <c r="E46" s="3">
         <v>303400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>378000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>421400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>399200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>419800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>439100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>472100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3">
         <v>1400</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>955000</v>
+      </c>
+      <c r="E47" s="3">
         <v>774900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>727300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>652400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>570600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>527600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>499900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>433000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>287500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E48" s="3">
         <v>97300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>95300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>94800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>93300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>92700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>94600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -2425,26 +2533,29 @@
       <c r="Q48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E49" s="3">
         <v>13500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>14100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2460,8 +2571,8 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,19 +2683,22 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E52" s="3">
         <v>19300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4900</v>
       </c>
       <c r="G52" s="3">
         <v>4900</v>
@@ -2587,14 +2707,14 @@
         <v>4900</v>
       </c>
       <c r="I52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J52" s="3">
         <v>16000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,55 +2783,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1483200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1208400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1220200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1187100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1082400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1045100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1049600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>981700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3">
         <v>288900</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,43 +2875,44 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1300</v>
+        <v>3100</v>
       </c>
       <c r="E57" s="3">
         <v>1300</v>
       </c>
       <c r="F57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G57" s="3">
         <v>3800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -2792,43 +2923,46 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>120800</v>
+      </c>
+      <c r="E58" s="3">
         <v>37700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>66100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>61800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>28000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2839,81 +2973,87 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E59" s="3">
         <v>36000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>64500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>77500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>58100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E60" s="3">
         <v>74900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>81600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>111700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>128000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>89000</v>
       </c>
       <c r="J60" s="3">
         <v>89000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
+      <c r="K60" s="3">
+        <v>89000</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
@@ -2921,47 +3061,50 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3">
         <v>200</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>445400</v>
+      </c>
+      <c r="E61" s="3">
         <v>324000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>327400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>240500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>213400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>92800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>96300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2980,55 +3123,61 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E62" s="3">
         <v>69400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>65100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>56800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>58800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>79400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>51500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3">
         <v>24600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,55 +3323,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>782100</v>
+      </c>
+      <c r="E66" s="3">
         <v>574400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>610000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>589700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>554400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>491600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>482400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>408900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3">
         <v>24800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3343,7 +3511,7 @@
         <v>74300</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,55 +3593,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-563900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-542600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-528200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-506500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-475200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-414200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-380200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-305400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
         <v>7300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,55 +3793,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>626800</v>
+      </c>
+      <c r="E76" s="3">
         <v>559700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>535900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>523200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>527900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>553500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>567200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>572800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3">
         <v>264200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-61000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-74800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-205700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-86500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,44 +4020,45 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E83" s="3">
         <v>6000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -3869,8 +4068,11 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,55 +4318,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E89" s="3">
         <v>18900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-23700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-25600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,41 +4390,42 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4217,8 +4438,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,55 +4538,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-230900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-96600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-125200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-91200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-99700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-73600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-87800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-104000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>48500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-190700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-287500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,67 +4808,73 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>298700</v>
+      </c>
+      <c r="E100" s="3">
         <v>12300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>63400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>110300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>103000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>46000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>37100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>354900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>24800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>20900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>243900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>289000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4641,8 +4890,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4659,51 +4908,57 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-61600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-47200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-62900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>225200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>85300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>51000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>62500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>700</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -656,125 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>250300</v>
+      </c>
+      <c r="E8" s="3">
         <v>245300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>218000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>211800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>195600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>186600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>192900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>204000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>352100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>154700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>136600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>183300</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
       <c r="P8" s="3">
         <v>0</v>
       </c>
@@ -784,47 +788,50 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>145600</v>
+      </c>
+      <c r="E9" s="3">
         <v>144900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>134500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>128800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>120600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>125100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>124700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>129100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>197300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>50800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>81700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>99800</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -834,47 +841,50 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E10" s="3">
         <v>100400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>83500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>83000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>75000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>61500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>68200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>74900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>154800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>103900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>54900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83500</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,47 +917,48 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E12" s="3">
         <v>19400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>88700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>14900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>11900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>39400</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -954,8 +968,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,8 +1021,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1127,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,108 +1147,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E17" s="3">
         <v>237600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>207400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>211600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>205900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>211600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>219600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>268100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>512700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>156900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>121800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>201700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>100</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-64100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-160600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-18400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-100</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,97 +1274,101 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-73200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-34400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-25600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-47300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-16900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-66900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-34700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-32800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-18800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-41900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-88400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-59200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-58000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-152900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-36900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1341,8 +1378,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1391,97 +1431,103 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-68200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-26700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-15000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-47100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-92000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-61400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-60900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-154000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-37200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7300</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>19500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7800</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1491,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-82700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-20000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-45900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-98600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-52200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-67000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-173600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-21200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-14400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-61000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-74800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-205700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-16500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-86500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,108 +1908,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E32" s="3">
         <v>34400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>25600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>47300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>16900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>66900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>34700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>32800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>18800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-21200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-14400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-61000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-74800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-205700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-16500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-86500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-21200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-14400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-61000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-74800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-205700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-16500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-86500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,58 +2222,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>233600</v>
+      </c>
+      <c r="E41" s="3">
         <v>274500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>186500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>252600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>304000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>289400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>309800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>327900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>415000</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3">
         <v>700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,46 +2326,49 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E43" s="3">
         <v>88700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>71800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>70200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>61700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>60200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>54600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2286,8 +2379,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,196 +2432,208 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E45" s="3">
         <v>35900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>53600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>47200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>48100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>56700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>17900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>361200</v>
+      </c>
+      <c r="E46" s="3">
         <v>399100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>303400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>378000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>421400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>399200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>419800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>439100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>472100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3">
         <v>1400</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>969300</v>
+      </c>
+      <c r="E47" s="3">
         <v>955000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>774900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>727300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>652400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>570600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>527600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>499900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>433000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>287500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E48" s="3">
         <v>96400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>97300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>95300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>94800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>93300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>92700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>94600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>66800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -2536,29 +2644,32 @@
       <c r="R48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E49" s="3">
         <v>12900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>14100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14300</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2574,8 +2685,8 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,22 +2803,25 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E52" s="3">
         <v>19900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>4900</v>
       </c>
       <c r="H52" s="3">
         <v>4900</v>
@@ -2710,14 +2830,14 @@
         <v>4900</v>
       </c>
       <c r="J52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K52" s="3">
         <v>16000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2736,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,58 +2909,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1453000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1483200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1208400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1220200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1187100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1082400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1045100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1049600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>981700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3">
         <v>288900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,46 +3006,47 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3100</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1300</v>
       </c>
       <c r="F57" s="3">
         <v>1300</v>
       </c>
       <c r="G57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H57" s="3">
         <v>3800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -2926,46 +3057,49 @@
       <c r="R57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E58" s="3">
         <v>120800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>37700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>44200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>66100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>45800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>61800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>28000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2976,87 +3110,93 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E59" s="3">
         <v>45400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>36100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>41800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>47200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>64500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>77500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>58100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>241300</v>
+      </c>
+      <c r="E60" s="3">
         <v>169400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>81600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>111700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>95700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>128000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>89000</v>
       </c>
       <c r="K60" s="3">
         <v>89000</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
+      <c r="L60" s="3">
+        <v>89000</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
@@ -3064,50 +3204,53 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3">
         <v>200</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>443800</v>
+      </c>
+      <c r="E61" s="3">
         <v>445400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>324000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>327400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>240500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>213400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>92800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>96300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3126,58 +3269,64 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E62" s="3">
         <v>68200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>69400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>65100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>57500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>56800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>58800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>51500</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>24600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,58 +3481,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>852700</v>
+      </c>
+      <c r="E66" s="3">
         <v>782100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>574400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>610000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>589700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>554400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>491600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>482400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>408900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3">
         <v>24800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3514,7 +3682,7 @@
         <v>74300</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,58 +3767,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-638600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-563900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-542600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-528200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-506500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-475200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-414200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-380200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-305400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3">
         <v>7300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,58 +3979,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>526000</v>
+      </c>
+      <c r="E76" s="3">
         <v>626800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>559700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>535900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>523200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>527900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>553500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>567200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>572800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3">
         <v>264200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-74800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-21200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-14400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-61000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-74800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-205700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-16500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-86500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,47 +4219,48 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -4071,8 +4270,11 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E89" s="3">
         <v>20500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-25600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,44 +4611,45 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -4441,8 +4662,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-120400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-230900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-96600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-91200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-99700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-73600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-87800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-104000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>48500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-190700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-287500</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,73 +5054,79 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E100" s="3">
         <v>298700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>63400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>110300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>103000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>46000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>37100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>354900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>20900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>243900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>289000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4893,8 +5142,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -4911,54 +5160,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="E102" s="3">
         <v>87500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-61600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-47200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-29700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-62900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>225200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>51000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>62500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>PGY</t>
   </si>
@@ -656,132 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>257200</v>
+      </c>
+      <c r="E8" s="3">
         <v>250300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>245300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>218000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>211800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>192900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>204000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>352100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>154700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>136600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183300</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3">
         <v>0</v>
       </c>
@@ -791,50 +795,53 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E9" s="3">
         <v>145600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>144900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>134500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>128800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>120600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>125100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>124700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>129100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>197300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>50800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>81700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>99800</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,50 +851,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E10" s="3">
         <v>104700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>83600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>83000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>75000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>61600</v>
+      </c>
+      <c r="K10" s="3">
+        <v>68200</v>
+      </c>
+      <c r="L10" s="3">
+        <v>74900</v>
+      </c>
+      <c r="M10" s="3">
+        <v>154800</v>
+      </c>
+      <c r="N10" s="3">
+        <v>103900</v>
+      </c>
+      <c r="O10" s="3">
+        <v>54900</v>
+      </c>
+      <c r="P10" s="3">
         <v>83500</v>
       </c>
-      <c r="G10" s="3">
-        <v>83000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>75000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>61500</v>
-      </c>
-      <c r="J10" s="3">
-        <v>68200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>74900</v>
-      </c>
-      <c r="L10" s="3">
-        <v>154800</v>
-      </c>
-      <c r="M10" s="3">
-        <v>103900</v>
-      </c>
-      <c r="N10" s="3">
-        <v>54900</v>
-      </c>
-      <c r="O10" s="3">
-        <v>83500</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,50 +931,51 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E12" s="3">
         <v>21900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>38600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>88700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>14900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>11900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>39400</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +985,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,31 +1041,34 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1077,31 +1097,34 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1130,8 +1153,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,114 +1174,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>234900</v>
+      </c>
+      <c r="E17" s="3">
         <v>245300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>237600</v>
       </c>
-      <c r="F17" s="3">
-        <v>207400</v>
-      </c>
       <c r="G17" s="3">
+        <v>207300</v>
+      </c>
+      <c r="H17" s="3">
         <v>211600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>205900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>211600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>219600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>268100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>512700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>156900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>121800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>201700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>100</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E18" s="3">
         <v>5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7700</v>
       </c>
-      <c r="F18" s="3">
-        <v>10600</v>
-      </c>
       <c r="G18" s="3">
+        <v>10800</v>
+      </c>
+      <c r="H18" s="3">
         <v>200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-10300</v>
-      </c>
       <c r="I18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-25000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-64100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-160600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-18400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,103 +1308,107 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-73200</v>
+        <v>108100</v>
       </c>
       <c r="E20" s="3">
-        <v>-34400</v>
+        <v>73200</v>
       </c>
       <c r="F20" s="3">
-        <v>-25600</v>
+        <v>34300</v>
       </c>
       <c r="G20" s="3">
-        <v>-47300</v>
+        <v>25600</v>
       </c>
       <c r="H20" s="3">
-        <v>-16900</v>
+        <v>47300</v>
       </c>
       <c r="I20" s="3">
-        <v>-66900</v>
+        <v>16900</v>
       </c>
       <c r="J20" s="3">
+        <v>67000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-34700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>6600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-32800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-85600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-61100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-20300</v>
       </c>
-      <c r="F21" s="3">
-        <v>-9000</v>
-      </c>
       <c r="G21" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="H21" s="3">
         <v>-41900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-88400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-59200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-58000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-152900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-36900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1381,31 +1418,34 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1434,103 +1474,109 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-68200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-26700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-15000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-47100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-92000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-61400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-60900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-154000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7300</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E24" s="3">
         <v>14500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>19500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7800</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-74200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-82700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-20000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-45900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-98600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-52200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-67000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-173600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7300</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-74800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-21200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-61000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-34000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-74800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-205700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-16500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-86500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7300</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,114 +1978,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>73200</v>
+        <v>-108100</v>
       </c>
       <c r="E32" s="3">
-        <v>34400</v>
+        <v>-73200</v>
       </c>
       <c r="F32" s="3">
-        <v>25600</v>
+        <v>-34300</v>
       </c>
       <c r="G32" s="3">
-        <v>47300</v>
+        <v>-25600</v>
       </c>
       <c r="H32" s="3">
-        <v>16900</v>
+        <v>-47300</v>
       </c>
       <c r="I32" s="3">
-        <v>66900</v>
+        <v>-16900</v>
       </c>
       <c r="J32" s="3">
+        <v>-67000</v>
+      </c>
+      <c r="K32" s="3">
         <v>34700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-6600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>32800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-74800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-21200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-61000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-74800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-205700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-16500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-86500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-74800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-21200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-61000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-74800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-205700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-16500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-86500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,84 +2309,88 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E41" s="3">
         <v>233600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>274500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>186500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>252600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>304000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>289400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>309800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>327900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>415000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>11300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2329,49 +2419,52 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>95100</v>
+        <v>113900</v>
       </c>
       <c r="E43" s="3">
-        <v>88700</v>
+        <v>99900</v>
       </c>
       <c r="F43" s="3">
-        <v>82000</v>
+        <v>87400</v>
       </c>
       <c r="G43" s="3">
-        <v>71800</v>
+        <v>87400</v>
       </c>
       <c r="H43" s="3">
-        <v>70200</v>
+        <v>71500</v>
       </c>
       <c r="I43" s="3">
-        <v>61700</v>
+        <v>68000</v>
       </c>
       <c r="J43" s="3">
+        <v>58500</v>
+      </c>
+      <c r="K43" s="3">
         <v>60200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>54600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2382,31 +2475,34 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2435,208 +2531,220 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>32500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>35900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>34900</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>53600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>47200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>48100</v>
-      </c>
-      <c r="J45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>49800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>56700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>298500</v>
+      </c>
+      <c r="E46" s="3">
         <v>361200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>399100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>303400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>378000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>421400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>399200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>419800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>439100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>472100</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3">
         <v>1400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>969300</v>
+        <v>937900</v>
       </c>
       <c r="E47" s="3">
-        <v>955000</v>
+        <v>936400</v>
       </c>
       <c r="F47" s="3">
-        <v>774900</v>
+        <v>919800</v>
       </c>
       <c r="G47" s="3">
-        <v>727300</v>
+        <v>740700</v>
       </c>
       <c r="H47" s="3">
-        <v>652400</v>
+        <v>692000</v>
       </c>
       <c r="I47" s="3">
-        <v>570600</v>
+        <v>614900</v>
       </c>
       <c r="J47" s="3">
+        <v>530800</v>
+      </c>
+      <c r="K47" s="3">
         <v>527600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>499900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>433000</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>287500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E48" s="3">
         <v>92300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>96400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>97300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>95300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>94800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>93300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>92700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>66800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -2647,32 +2755,35 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E49" s="3">
         <v>12200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14300</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2799,8 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,25 +2923,28 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E52" s="3">
         <v>18000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5500</v>
-      </c>
-      <c r="H52" s="3">
-        <v>4900</v>
       </c>
       <c r="I52" s="3">
         <v>4900</v>
@@ -2833,14 +2953,14 @@
         <v>4900</v>
       </c>
       <c r="K52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L52" s="3">
         <v>16000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9900</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,61 +3035,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1370800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1453000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1483200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1208400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1220200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1187100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1082400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1045100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1049600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>981700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3">
         <v>288900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,49 +3137,50 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E57" s="3">
         <v>7300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3100</v>
-      </c>
-      <c r="F57" s="3">
-        <v>1300</v>
       </c>
       <c r="G57" s="3">
         <v>1300</v>
       </c>
       <c r="H57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I57" s="3">
         <v>3800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3060,49 +3191,52 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>189000</v>
+        <v>213700</v>
       </c>
       <c r="E58" s="3">
-        <v>120800</v>
+        <v>195400</v>
       </c>
       <c r="F58" s="3">
-        <v>37700</v>
+        <v>127500</v>
       </c>
       <c r="G58" s="3">
-        <v>44200</v>
+        <v>44600</v>
       </c>
       <c r="H58" s="3">
-        <v>66100</v>
+        <v>50400</v>
       </c>
       <c r="I58" s="3">
-        <v>45800</v>
+        <v>73300</v>
       </c>
       <c r="J58" s="3">
+        <v>53800</v>
+      </c>
+      <c r="K58" s="3">
         <v>61800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>28000</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3113,93 +3247,99 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45000</v>
+        <v>2400</v>
       </c>
       <c r="E59" s="3">
-        <v>45400</v>
+        <v>2500</v>
       </c>
       <c r="F59" s="3">
-        <v>36000</v>
+        <v>2100</v>
       </c>
       <c r="G59" s="3">
-        <v>36100</v>
+        <v>18700</v>
       </c>
       <c r="H59" s="3">
-        <v>41800</v>
+        <v>600</v>
       </c>
       <c r="I59" s="3">
-        <v>47200</v>
+        <v>6200</v>
       </c>
       <c r="J59" s="3">
+        <v>11700</v>
+      </c>
+      <c r="K59" s="3">
         <v>64500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>77500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>58100</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>254500</v>
+      </c>
+      <c r="E60" s="3">
         <v>241300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>169400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>81600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>111700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>128000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>89000</v>
       </c>
       <c r="L60" s="3">
         <v>89000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
+      <c r="M60" s="3">
+        <v>89000</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
@@ -3207,53 +3347,56 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
         <v>200</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>443800</v>
+        <v>473400</v>
       </c>
       <c r="E61" s="3">
-        <v>445400</v>
+        <v>483400</v>
       </c>
       <c r="F61" s="3">
-        <v>324000</v>
+        <v>487200</v>
       </c>
       <c r="G61" s="3">
-        <v>327400</v>
+        <v>368000</v>
       </c>
       <c r="H61" s="3">
-        <v>240500</v>
+        <v>368500</v>
       </c>
       <c r="I61" s="3">
-        <v>213400</v>
+        <v>284400</v>
       </c>
       <c r="J61" s="3">
+        <v>259800</v>
+      </c>
+      <c r="K61" s="3">
         <v>92800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>87500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>96300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3272,61 +3415,67 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>78100</v>
+        <v>25700</v>
       </c>
       <c r="E62" s="3">
-        <v>68200</v>
+        <v>38400</v>
       </c>
       <c r="F62" s="3">
-        <v>69400</v>
+        <v>26300</v>
       </c>
       <c r="G62" s="3">
-        <v>65100</v>
+        <v>25400</v>
       </c>
       <c r="H62" s="3">
-        <v>57500</v>
+        <v>23400</v>
       </c>
       <c r="I62" s="3">
-        <v>56800</v>
+        <v>13000</v>
       </c>
       <c r="J62" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K62" s="3">
         <v>58800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>79400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3">
         <v>24600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,61 +3639,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>852700</v>
+        <v>753800</v>
       </c>
       <c r="E66" s="3">
-        <v>782100</v>
+        <v>763200</v>
       </c>
       <c r="F66" s="3">
-        <v>574400</v>
+        <v>683000</v>
       </c>
       <c r="G66" s="3">
-        <v>610000</v>
+        <v>468400</v>
       </c>
       <c r="H66" s="3">
-        <v>589700</v>
+        <v>474100</v>
       </c>
       <c r="I66" s="3">
-        <v>554400</v>
+        <v>409700</v>
       </c>
       <c r="J66" s="3">
+        <v>365900</v>
+      </c>
+      <c r="K66" s="3">
         <v>491600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>482400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>408900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3">
         <v>24800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3685,7 +3853,7 @@
         <v>74300</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,61 +3941,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-706100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-638600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-563900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-542600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-528200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-506500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-475200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-414200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-380200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-305400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>7300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,61 +4165,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>462300</v>
+      </c>
+      <c r="E76" s="3">
         <v>526000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>626800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>559700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>535900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>523200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>527900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>553500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>567200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>572800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3">
         <v>264200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-74800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-21200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-61000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-74800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-205700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-16500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-86500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,50 +4418,51 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7000</v>
+        <v>-6700</v>
       </c>
       <c r="E83" s="3">
-        <v>6300</v>
+        <v>4500</v>
       </c>
       <c r="F83" s="3">
-        <v>6000</v>
+        <v>3500</v>
       </c>
       <c r="G83" s="3">
-        <v>5200</v>
+        <v>2200</v>
       </c>
       <c r="H83" s="3">
-        <v>4500</v>
+        <v>2900</v>
       </c>
       <c r="I83" s="3">
-        <v>3500</v>
+        <v>700</v>
       </c>
       <c r="J83" s="3">
+        <v>500</v>
+      </c>
+      <c r="K83" s="3">
         <v>2200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -4273,8 +4472,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E89" s="3">
         <v>15500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>20500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-23700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-25600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,47 +4832,48 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -4665,8 +4886,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +4998,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-111400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-120400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-230900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-96600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-125200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-91200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-99700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-73600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-87800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-104000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>48500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-190700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-287500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,31 +5078,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,75 +5300,81 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E100" s="3">
         <v>63700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>298700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>63400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>110300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>103000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>46000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>37100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>354900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>24800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>20900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>243900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>289000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-900</v>
+        <v>-1500</v>
       </c>
       <c r="E101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="F101" s="3">
-        <v>3700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-1500</v>
+        <v>-2700</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -5145,8 +5394,8 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -5163,57 +5412,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-86900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-42100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>87500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-61600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-47200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-29700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-62900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>225200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>51000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>62500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>PGY</t>
   </si>
@@ -656,139 +656,142 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>279400</v>
+      </c>
+      <c r="E8" s="3">
         <v>257200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>250300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>245300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>218000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>211800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>195600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>186600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>192900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>204000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>352100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>154700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>136600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>183300</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
@@ -798,53 +801,56 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>158200</v>
+      </c>
+      <c r="E9" s="3">
         <v>149000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>145600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>144900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>134500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>128800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>120600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>125100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>124700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>129100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>197300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>50800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>81700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>99800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,53 +860,56 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>121200</v>
+      </c>
+      <c r="E10" s="3">
         <v>108300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>104700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>83600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>83000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>61600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>68200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>103900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>54900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>83500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,8 +919,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,53 +944,54 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E12" s="3">
         <v>16700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>38600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>88700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>14900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>39400</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +1001,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,13 +1060,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>10200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1058,8 +1077,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>100</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1070,8 +1089,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1100,35 +1119,38 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6300</v>
       </c>
-      <c r="G15" s="3">
-        <v>6000</v>
-      </c>
       <c r="H15" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I15" s="3">
         <v>5200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1156,8 +1178,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1200,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>243600</v>
+      </c>
+      <c r="E17" s="3">
         <v>234900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>245300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>237600</v>
       </c>
-      <c r="G17" s="3">
-        <v>207300</v>
-      </c>
       <c r="H17" s="3">
+        <v>207400</v>
+      </c>
+      <c r="I17" s="3">
         <v>211600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>205900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>211600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>219600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>268100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>512700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>156900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>121800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>201700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E18" s="3">
         <v>22400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7700</v>
       </c>
-      <c r="G18" s="3">
-        <v>10800</v>
-      </c>
       <c r="H18" s="3">
+        <v>10700</v>
+      </c>
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-25000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-160600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-18400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-100</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,109 +1341,113 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>266200</v>
+      </c>
+      <c r="E20" s="3">
         <v>108100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>73200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>34300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>25600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>47300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>67000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-34700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>6600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-32800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-85600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-61100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-20300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-8900</v>
-      </c>
       <c r="H21" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-41900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-22700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-88400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-59200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-58000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-152900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-36900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1421,8 +1457,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1447,8 +1486,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1477,109 +1516,115 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-240500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-85800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-68200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-26700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-15000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-47100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-92000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-61400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-60900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-154000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7300</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>19500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7800</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1589,8 +1634,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1693,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-257100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-74200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-82700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-20000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-45900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-98600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-52200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-67000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-173600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7300</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-237900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-67500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-74800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-21200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-61000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-34000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-74800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-205700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-86500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7300</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1870,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1929,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1988,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,120 +2047,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-266200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-108100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-73200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-34300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-25600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-47300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-67000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>34700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-6600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>32800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-237900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-67500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-74800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-21200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-61000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-74800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-205700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-86500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7300</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2224,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-237900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-67500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-74800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-21200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-61000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-74800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-205700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-86500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7300</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2372,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,91 +2395,95 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>187900</v>
+      </c>
+      <c r="E41" s="3">
         <v>147100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>233600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>274500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>186500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>252600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>304000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>289400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>309800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>327900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>415000</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
         <v>700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E42" s="3">
         <v>11300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2422,52 +2511,55 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127400</v>
+      </c>
+      <c r="E43" s="3">
         <v>113900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99900</v>
-      </c>
-      <c r="F43" s="3">
-        <v>87400</v>
       </c>
       <c r="G43" s="3">
         <v>87400</v>
       </c>
       <c r="H43" s="3">
+        <v>87400</v>
+      </c>
+      <c r="I43" s="3">
         <v>71500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>68000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>60200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>54600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -2478,8 +2570,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2504,8 +2599,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2534,13 +2629,16 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>2200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2548,206 +2646,215 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>3400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>49800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>56700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>800</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>351500</v>
+      </c>
+      <c r="E46" s="3">
         <v>298500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>361200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>399100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>303400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>378000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>421400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>399200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>419800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>439100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>472100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3">
         <v>1400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>778300</v>
+      </c>
+      <c r="E47" s="3">
         <v>937900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>936400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>919800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>740700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>692000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>614900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>530800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>527600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>499900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>433000</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>287500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E48" s="3">
         <v>73400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>92300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>96400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>97300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>95300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>94800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>93300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>92700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>94600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>66800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -2758,35 +2865,38 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E49" s="3">
         <v>11600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2802,8 +2912,8 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2814,8 +2924,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2983,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,28 +3042,31 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E52" s="3">
         <v>17400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>4900</v>
       </c>
       <c r="J52" s="3">
         <v>4900</v>
@@ -2956,14 +3075,14 @@
         <v>4900</v>
       </c>
       <c r="L52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M52" s="3">
         <v>16000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9900</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2982,8 +3101,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3160,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1291100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1370800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1453000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1483200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1208400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1220200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1187100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1082400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1045100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1049600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>981700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3">
         <v>288900</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3244,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,52 +3267,53 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1300</v>
       </c>
       <c r="H57" s="3">
         <v>1300</v>
       </c>
       <c r="I57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J57" s="3">
         <v>3800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2900</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3194,52 +3324,55 @@
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E58" s="3">
         <v>213700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>195400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>127500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>50400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>73300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>53800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>61800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>28000</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3250,99 +3383,105 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>64500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>58100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>195500</v>
+      </c>
+      <c r="E60" s="3">
         <v>254500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>241300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>169400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>74900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>81600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>111700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>95700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>128000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>89000</v>
       </c>
       <c r="M60" s="3">
         <v>89000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
+      <c r="N60" s="3">
+        <v>89000</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
@@ -3350,56 +3489,59 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3">
         <v>200</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>547500</v>
+      </c>
+      <c r="E61" s="3">
         <v>473400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>483400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>487200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>368000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>368500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>284400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>259800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>92800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>87500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>96300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3418,64 +3560,70 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E62" s="3">
         <v>25700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>38400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>26300</v>
       </c>
-      <c r="G62" s="3">
-        <v>25400</v>
-      </c>
       <c r="H62" s="3">
+        <v>25500</v>
+      </c>
+      <c r="I62" s="3">
         <v>23400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>58800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>79400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>24600</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3678,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3737,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3796,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>775300</v>
+      </c>
+      <c r="E66" s="3">
         <v>753800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>763200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>683000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>468400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>474100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>409700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>365900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>491600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>482400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>408900</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3">
         <v>24800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3880,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3937,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3996,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3856,7 +4023,7 @@
         <v>74300</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3888,8 +4055,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,64 +4114,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-944000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-706100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-638600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-563900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-542600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-528200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-506500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-475200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-414200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-380200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-305400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>7300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4232,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4291,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,64 +4350,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>326500</v>
+      </c>
+      <c r="E76" s="3">
         <v>462300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>526000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>626800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>559700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>535900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>523200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>527900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>553500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>567200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>572800</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3">
         <v>264200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4468,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-237900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-67500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-74800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-21200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-61000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-74800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-205700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-86500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7300</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,53 +4616,54 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E83" s="3">
         <v>-6700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -4475,8 +4673,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4732,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4791,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4850,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4909,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4968,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-25600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,50 +5052,51 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -4889,8 +5109,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5168,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,64 +5227,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-111400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-120400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-230900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-96600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-125200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-91200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-99700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-73600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-87800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-104000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>48500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-190700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-287500</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5311,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5105,8 +5338,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5135,8 +5368,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5427,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5486,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,76 +5545,82 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E100" s="3">
         <v>25500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>63700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>298700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>63400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>110300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>103000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>46000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>37100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>354900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>24800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>20900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>243900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>289000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2700</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5397,8 +5645,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -5415,60 +5663,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-86900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-42100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>87500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-61600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-47200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-29700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-62900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>225200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>85300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>51000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>62500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>PGY</t>
   </si>
@@ -656,145 +656,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E8" s="3">
         <v>279400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>257200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>250300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>245300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>218000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>211800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>195600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>192900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>204000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>352100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>154700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>136600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>183300</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
         <v>0</v>
       </c>
@@ -804,56 +808,59 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E9" s="3">
         <v>158200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>149000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>145600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>144900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>134500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>128800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>120600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>125100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>124700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>129100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>197300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>50800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>81700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>99800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -863,56 +870,59 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E10" s="3">
         <v>121200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>108300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>104700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>83600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>83000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>61600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>154800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>103900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>54900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>83500</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,56 +958,57 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E12" s="3">
         <v>18600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>23600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>38600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>88700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>39400</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1004,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,17 +1080,20 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1092,8 +1112,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1122,38 +1142,41 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E15" s="3">
         <v>28400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>242300</v>
+      </c>
+      <c r="E17" s="3">
         <v>243600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>234900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>245300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>237600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>207400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>211600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>205900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>211600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>219600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>268100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>512700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>156900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>121800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>201700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E18" s="3">
         <v>35800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-25000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-26700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-64100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-160600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-18400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,115 +1375,119 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E20" s="3">
         <v>266200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>108100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>73200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>34300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>25600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>47300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>16900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>67000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-34700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>6600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-202000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-85600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-61100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-20300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-41900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-22700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-88400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-59200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-58000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-152900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-36900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1460,8 +1497,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1489,8 +1529,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1519,115 +1559,121 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-240500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-85800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-68200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-26700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-47100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-92000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-61400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-60900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-154000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-37200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>16600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-9200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>19500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7800</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -1637,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-257100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-74200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-82700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-20000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-45900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-32100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-98600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-52200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-67000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-173600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-45000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-237900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-67500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-74800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-21200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-61000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-34000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-74800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-205700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-86500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,126 +2117,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-47700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-266200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-108100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-73200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-34300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-25600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-47300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-16900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-67000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>34700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-6600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>32800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-237900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-67500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-74800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-21200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-61000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-74800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-205700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-86500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-237900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-67500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-74800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-21200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-61000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-74800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-205700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-86500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,97 +2482,101 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>186800</v>
+      </c>
+      <c r="E41" s="3">
         <v>187900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>147100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>233600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>274500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>186500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>252600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>304000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>289400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>309800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>327900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>415000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3">
         <v>700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E42" s="3">
         <v>7800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3300</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2514,55 +2604,58 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E43" s="3">
         <v>127400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99900</v>
-      </c>
-      <c r="G43" s="3">
-        <v>87400</v>
       </c>
       <c r="H43" s="3">
         <v>87400</v>
       </c>
       <c r="I43" s="3">
+        <v>87400</v>
+      </c>
+      <c r="J43" s="3">
         <v>71500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>68000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>60200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>54600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39200</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
+      <c r="R43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -2573,8 +2666,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2602,8 +2698,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2632,232 +2728,244 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>49800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>56700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>355600</v>
+      </c>
+      <c r="E46" s="3">
         <v>351500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>298500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>361200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>399100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>303400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>378000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>421400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>399200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>419800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>439100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>472100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3">
         <v>1400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>762400</v>
+      </c>
+      <c r="E47" s="3">
         <v>778300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>937900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>936400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>919800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>740700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>692000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>614900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>530800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>527600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>499900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>433000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>287500</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E48" s="3">
         <v>74900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>92300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>96400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>97300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>95300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>94800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>93300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>92700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>66800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R48" s="3">
-        <v>0</v>
+      <c r="R48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S48" s="3">
         <v>0</v>
@@ -2868,38 +2976,41 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E49" s="3">
         <v>35900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14300</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2915,8 +3026,8 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2927,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,31 +3162,34 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E52" s="3">
         <v>21400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>4900</v>
       </c>
       <c r="K52" s="3">
         <v>4900</v>
@@ -3078,14 +3198,14 @@
         <v>4900</v>
       </c>
       <c r="M52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N52" s="3">
         <v>16000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9900</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,67 +3286,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1278400</v>
+      </c>
+      <c r="E54" s="3">
         <v>1291100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1370800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1453000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1483200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1208400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1220200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1187100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1082400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1045100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1049600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>981700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3">
         <v>288900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,55 +3398,56 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1300</v>
       </c>
       <c r="I57" s="3">
         <v>1300</v>
       </c>
       <c r="J57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K57" s="3">
         <v>3800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2900</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3327,55 +3458,58 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>142400</v>
+      </c>
+      <c r="E58" s="3">
         <v>133300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>213700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>195400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>127500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>50400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>73300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>53800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3386,105 +3520,111 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E59" s="3">
         <v>38900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>64500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>58100</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>198700</v>
+      </c>
+      <c r="E60" s="3">
         <v>195500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>254500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>241300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>169400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>81600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>111700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>95700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>128000</v>
-      </c>
-      <c r="M60" s="3">
-        <v>89000</v>
       </c>
       <c r="N60" s="3">
         <v>89000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
+      <c r="O60" s="3">
+        <v>89000</v>
       </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
@@ -3492,59 +3632,62 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3">
         <v>200</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>536400</v>
+      </c>
+      <c r="E61" s="3">
         <v>547500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>473400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>483400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>487200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>368000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>368500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>284400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>259800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>92800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>87500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>96300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3563,67 +3706,73 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E62" s="3">
         <v>32300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>58800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3">
         <v>24600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,67 +3954,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>763300</v>
+      </c>
+      <c r="E66" s="3">
         <v>775300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>753800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>763200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>683000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>468400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>474100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>409700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>365900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>491600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>482400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>408900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3">
         <v>24800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4026,7 +4194,7 @@
         <v>74300</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,67 +4288,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-936200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-944000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-706100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-638600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-563900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-542600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-528200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-506500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-475200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-414200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-380200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-305400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3">
         <v>7300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,67 +4536,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>335500</v>
+      </c>
+      <c r="E76" s="3">
         <v>326500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>462300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>526000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>626800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>559700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>535900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>523200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>527900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>553500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>567200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>572800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3">
         <v>264200</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-237900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-67500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-74800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-21200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-61000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-74800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-205700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-86500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,56 +4815,57 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>17900</v>
+        <v>6300</v>
       </c>
       <c r="E83" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F83" s="3">
         <v>-6700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -4676,8 +4875,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E89" s="3">
         <v>32100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15500</v>
       </c>
-      <c r="G89" s="3">
-        <v>20500</v>
-      </c>
       <c r="H89" s="3">
+        <v>17700</v>
+      </c>
+      <c r="I89" s="3">
         <v>18900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-25600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,53 +5273,54 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5112,8 +5333,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-36000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-111400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-120400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-230900</v>
-      </c>
       <c r="H94" s="3">
+        <v>-228100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-96600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-125200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-91200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-99700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-73600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-87800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-104000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>48500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-190700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-287500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5341,8 +5575,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5371,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,82 +5791,88 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E100" s="3">
         <v>48800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>25500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>63700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>298700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>63400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>110300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>103000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>46000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>37100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>354900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>20900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>243900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>289000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>3700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5648,8 +5897,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5666,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>45500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-86900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-42100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>87500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-61600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-47200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-62900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>225200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>85300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>51000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>62500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="92">
   <si>
     <t>PGY</t>
   </si>
@@ -656,152 +656,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E8" s="3">
         <v>290000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>279400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>257200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>250300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>245300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>218000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>211800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>195600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>192900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>204000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>352100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>154700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>136600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>183300</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
@@ -811,59 +815,62 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E9" s="3">
         <v>167100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>158200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>149000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>145600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>144900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>134500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>128800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>120600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>125100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>124700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>129100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>197300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>50800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>81700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>99800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,59 +880,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E10" s="3">
         <v>122900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>121200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>108300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>104700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>83600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>83000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>61600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>68200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>154800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>103900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>54900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>83500</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,59 +972,60 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E12" s="3">
         <v>19400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>17600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>23600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>38600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>88700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>39400</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,20 +1100,23 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>10200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,8 +1135,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1145,41 +1165,44 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E15" s="3">
         <v>7700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>28400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3500</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>269900</v>
+      </c>
+      <c r="E17" s="3">
         <v>242300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>243600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>234900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>245300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>237600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>207400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>211600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>205900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>211600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>219600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>268100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>512700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>156900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>121800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>201700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E18" s="3">
         <v>47700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>35800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>22400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>10700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-25000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-64100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-160600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-18400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,121 +1409,125 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E20" s="3">
         <v>47700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>266200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>108100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>73200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>34300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>25600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>47300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>67000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-32800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>7400</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E21" s="3">
         <v>7700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-202000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-85600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-61100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-41900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-22700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-88400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-59200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-58000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-152900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-36900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1537,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1532,8 +1572,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1562,121 +1602,127 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-240500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-85800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-68200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-26700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-15000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-47100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-92000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-61400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-60900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-154000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-37200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-11500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-9200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>19500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7800</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-257100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-74200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-82700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-20000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-32100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-98600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-67000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-173600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7300</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E27" s="3">
         <v>7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-237900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-67500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-74800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-21200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-61000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-34000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-74800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-205700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-86500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7300</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-34900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-47700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-266200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-108100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-73200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-34300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-25600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-47300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-67000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>32800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-7400</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E33" s="3">
         <v>7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-237900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-67500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-74800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-21200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-61000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-34000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-74800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-205700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-86500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7300</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E35" s="3">
         <v>7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-237900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-67500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-74800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-21200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-61000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-34000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-74800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-205700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-86500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7300</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,103 +2569,107 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E41" s="3">
         <v>186800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>187900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>147100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>233600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>274500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>186500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>252600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>304000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>289400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>309800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>327900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>415000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3">
         <v>700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E42" s="3">
         <v>19700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2607,58 +2697,61 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E43" s="3">
         <v>107500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>87400</v>
       </c>
       <c r="I43" s="3">
         <v>87400</v>
       </c>
       <c r="J43" s="3">
+        <v>87400</v>
+      </c>
+      <c r="K43" s="3">
         <v>71500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>68000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>60200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2701,8 +2797,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2731,244 +2827,256 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>2200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>49800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17900</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>362500</v>
+      </c>
+      <c r="E46" s="3">
         <v>355600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>351500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>298500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>361200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>399100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>303400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>378000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>421400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>399200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>419800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>439100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>472100</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3">
         <v>1400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>868000</v>
+      </c>
+      <c r="E47" s="3">
         <v>762400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>778300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>937900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>936400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>919800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>740700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>692000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>614900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>530800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>527600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>499900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>433000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3">
         <v>287500</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E48" s="3">
         <v>71500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>74900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>92300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>96400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>97300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>95300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>94800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>93300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>92700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>94600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>66800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2979,41 +3087,44 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E49" s="3">
         <v>34600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>35900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3140,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,34 +3282,37 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E52" s="3">
         <v>25900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>19900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>19300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5500</v>
-      </c>
-      <c r="K52" s="3">
-        <v>4900</v>
       </c>
       <c r="L52" s="3">
         <v>4900</v>
@@ -3201,14 +3321,14 @@
         <v>4900</v>
       </c>
       <c r="N52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O52" s="3">
         <v>16000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9900</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1278400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1291100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1370800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1453000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1483200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1208400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1220200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1187100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1082400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1045100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1049600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>981700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3">
         <v>288900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,58 +3529,59 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E57" s="3">
         <v>10000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1300</v>
       </c>
       <c r="J57" s="3">
         <v>1300</v>
       </c>
       <c r="K57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L57" s="3">
         <v>3800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3461,58 +3592,61 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>190100</v>
+      </c>
+      <c r="E58" s="3">
         <v>142400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>133300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>213700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>195400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>127500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>73300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>53800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>61800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>28000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3523,111 +3657,117 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>38900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>64500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>58100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>254500</v>
+      </c>
+      <c r="E60" s="3">
         <v>198700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>195500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>254500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>241300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>169400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>81600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>111700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>95700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>128000</v>
-      </c>
-      <c r="N60" s="3">
-        <v>89000</v>
       </c>
       <c r="O60" s="3">
         <v>89000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
+      <c r="P60" s="3">
+        <v>89000</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
@@ -3635,62 +3775,65 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3">
         <v>200</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>573600</v>
+      </c>
+      <c r="E61" s="3">
         <v>536400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>547500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>473400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>483400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>487200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>368000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>368500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>284400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>259800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>92800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>87500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>96300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3709,70 +3852,76 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E62" s="3">
         <v>28300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>32300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>38400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>58800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>79400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>51500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3">
         <v>24600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>856800</v>
+      </c>
+      <c r="E66" s="3">
         <v>763300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>775300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>753800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>763200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>683000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>468400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>474100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>409700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>365900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>491600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>482400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>408900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3">
         <v>24800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4197,7 +4365,7 @@
         <v>74300</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-919500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-936200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-944000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-706100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-638600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-563900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-542600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-528200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-506500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-475200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-414200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-380200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-305400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3">
         <v>7300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>366800</v>
+      </c>
+      <c r="E76" s="3">
         <v>335500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>326500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>462300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>526000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>626800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>559700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>535900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>523200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>527900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>553500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>567200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>572800</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3">
         <v>264200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E81" s="3">
         <v>7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-237900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-67500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-74800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-21200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-61000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-34000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-74800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-205700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-86500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7300</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,59 +5014,60 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E83" s="3">
         <v>6300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>15300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-6700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E89" s="3">
         <v>34400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>32100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
-        <v>15500</v>
-      </c>
       <c r="H89" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I89" s="3">
         <v>17700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-25600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5283,47 +5504,47 @@
         <v>-3800</v>
       </c>
       <c r="E91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-125300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-36000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-111400</v>
       </c>
-      <c r="G94" s="3">
-        <v>-120400</v>
-      </c>
       <c r="H94" s="3">
+        <v>-114200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-228100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-96600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-125200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-91200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-99700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-73600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-87800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-104000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>48500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-190700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-287500</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5578,8 +5812,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,88 +6037,94 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>78400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>48800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>25500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>63700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>298700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>63400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>110300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>103000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>46000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>37100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>354900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>24800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>20900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>243900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>289000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5900,8 +6149,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5918,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E102" s="3">
         <v>3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>45500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-86900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-42100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>87500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-61600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-47200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-29700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-62900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>225200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>85300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>51000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>62500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>PGY</t>
   </si>
@@ -656,166 +656,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>334800</v>
+      </c>
+      <c r="E8" s="3">
         <v>350200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>326400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>290000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>279400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>257200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>250300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>245300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>218000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>211800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>195600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>186600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>192900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>204000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>352100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>154700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>136600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>183300</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
@@ -825,65 +828,68 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E9" s="3">
         <v>200600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>191500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>167100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>158200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>149000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>145600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>144900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>134500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>128800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>120600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>125100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>124700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>129100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>197300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>50800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>81700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>99800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -893,65 +899,68 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>144800</v>
+      </c>
+      <c r="E10" s="3">
         <v>149600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>134900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>122900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>121200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>108300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>104700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>100400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>83600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>83000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>61600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>74900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>154800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>103900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>54900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>83500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,8 +970,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,65 +999,66 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E12" s="3">
         <v>18200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>19400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>16700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>21100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>38600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>88700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>39400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,8 +1068,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,29 +1139,32 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E14" s="3">
         <v>44500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>10200</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>256300</v>
+      </c>
+      <c r="I14" s="3">
         <v>77800</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,8 +1180,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1191,47 +1210,50 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7700</v>
       </c>
-      <c r="G15" s="3">
-        <v>28400</v>
-      </c>
       <c r="H15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I15" s="3">
         <v>500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1259,8 +1281,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,144 +1307,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>255100</v>
+      </c>
+      <c r="E17" s="3">
         <v>270200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>269900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>242300</v>
       </c>
-      <c r="G17" s="3">
-        <v>243600</v>
-      </c>
       <c r="H17" s="3">
+        <v>247600</v>
+      </c>
+      <c r="I17" s="3">
         <v>234900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>245300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>237600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>207400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>211600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>205900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>211600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>219600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>268100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>512700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>156900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>121800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>201700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E18" s="3">
         <v>80000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>56500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47700</v>
       </c>
-      <c r="G18" s="3">
-        <v>35800</v>
-      </c>
       <c r="H18" s="3">
+        <v>31800</v>
+      </c>
+      <c r="I18" s="3">
         <v>22400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-25000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-26700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-64100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-160600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,133 +1476,137 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E20" s="3">
         <v>27400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>34900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>47700</v>
       </c>
-      <c r="G20" s="3">
-        <v>266200</v>
-      </c>
       <c r="H20" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I20" s="3">
         <v>30300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>73200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>34300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>25600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>47300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>67000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-34700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-32800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E21" s="3">
         <v>54400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7700</v>
       </c>
-      <c r="G21" s="3">
-        <v>-202000</v>
-      </c>
       <c r="H21" s="3">
+        <v>17700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-7400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-61100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-41900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-22700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-88400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-59200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-58000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-152900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-17800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-36900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1616,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1618,8 +1657,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1648,133 +1687,139 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E23" s="3">
         <v>8100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21500</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
         <v>-240500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-85800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-68200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-47100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-92000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-61400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-154000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-18000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-37200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-15200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-11500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-9200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7800</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
@@ -1784,8 +1829,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1900,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E26" s="3">
         <v>23300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-257100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-74200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-82700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-20000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-32100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-98600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-52200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-173600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-45000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7300</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E27" s="3">
         <v>21300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-237900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-67500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-74800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-61000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-34000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-74800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-205700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-86500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7300</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2113,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2184,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2255,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,144 +2326,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-27400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-34900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-47700</v>
       </c>
-      <c r="G32" s="3">
-        <v>-266200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="I32" s="3">
         <v>-30300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-73200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-34300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-25600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-47300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-67000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>34700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>32800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E33" s="3">
         <v>22500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-237900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-67500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-74800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-61000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-74800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-205700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-86500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7300</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2539,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E35" s="3">
         <v>22500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-237900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-67500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-74800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-61000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-74800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-205700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-86500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7300</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2715,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,115 +2742,119 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>235300</v>
+      </c>
+      <c r="E41" s="3">
         <v>218300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>183000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>186800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>187900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>147100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>233600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>274500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>186500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>252600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>304000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>289400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>309800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>327900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>415000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3">
         <v>700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>945300</v>
       </c>
       <c r="E42" s="3">
+        <v>887700</v>
+      </c>
+      <c r="F42" s="3">
         <v>21500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>19700</v>
       </c>
-      <c r="G42" s="3">
-        <v>7800</v>
-      </c>
       <c r="H42" s="3">
+        <v>778400</v>
+      </c>
+      <c r="I42" s="3">
         <v>11300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3300</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2793,64 +2882,67 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>166300</v>
+      </c>
+      <c r="E43" s="3">
         <v>155000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>118500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107500</v>
       </c>
-      <c r="G43" s="3">
-        <v>127400</v>
-      </c>
       <c r="H43" s="3">
+        <v>127100</v>
+      </c>
+      <c r="I43" s="3">
         <v>113900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99900</v>
-      </c>
-      <c r="J43" s="3">
-        <v>87400</v>
       </c>
       <c r="K43" s="3">
         <v>87400</v>
       </c>
       <c r="L43" s="3">
+        <v>87400</v>
+      </c>
+      <c r="M43" s="3">
         <v>71500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>68000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>58500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>39200</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2861,8 +2953,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2899,8 +2994,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2929,8 +3024,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2943,8 +3041,8 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
-        <v>2200</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -2955,242 +3053,251 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>49800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>56700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3">
         <v>800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>419700</v>
+        <v>1406800</v>
       </c>
       <c r="E46" s="3">
+        <v>1307500</v>
+      </c>
+      <c r="F46" s="3">
         <v>362500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>355600</v>
       </c>
-      <c r="G46" s="3">
-        <v>351500</v>
-      </c>
       <c r="H46" s="3">
+        <v>1139600</v>
+      </c>
+      <c r="I46" s="3">
         <v>298500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>361200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>399100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>303400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>378000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>421400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>399200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>419800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>439100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>472100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3">
         <v>1400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>902600</v>
+        <v>13500</v>
       </c>
       <c r="E47" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F47" s="3">
         <v>868000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>762400</v>
       </c>
-      <c r="G47" s="3">
-        <v>778300</v>
-      </c>
       <c r="H47" s="3">
+        <v>21900</v>
+      </c>
+      <c r="I47" s="3">
         <v>937900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>936400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>919800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>740700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>692000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>614900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>530800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>527600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>499900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>433000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3">
         <v>287500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E48" s="3">
         <v>64600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>68200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>71500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>74900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>92300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>96400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>97300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>95300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>94800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>93300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>92700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>94600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>66800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
@@ -3201,47 +3308,50 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E49" s="3">
         <v>32000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>34600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>35900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3257,8 +3367,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3269,8 +3379,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3450,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,40 +3521,43 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E52" s="3">
         <v>36500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25900</v>
       </c>
-      <c r="G52" s="3">
-        <v>21400</v>
-      </c>
       <c r="H52" s="3">
+        <v>18800</v>
+      </c>
+      <c r="I52" s="3">
         <v>17400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4900</v>
       </c>
       <c r="N52" s="3">
         <v>4900</v>
@@ -3447,14 +3566,14 @@
         <v>4900</v>
       </c>
       <c r="P52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="Q52" s="3">
         <v>16000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9900</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3592,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,76 +3663,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1545900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1455400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1399000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1278400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1291100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1370800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1453000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1483200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1208400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1220200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1187100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1082400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1045100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1049600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>981700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3">
         <v>288900</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3763,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,64 +3790,65 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>5100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1300</v>
       </c>
       <c r="L57" s="3">
         <v>1300</v>
       </c>
       <c r="M57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N57" s="3">
         <v>3800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -3729,64 +3859,67 @@
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>190100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>142400</v>
       </c>
-      <c r="G58" s="3">
-        <v>133300</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>213700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>195400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>127500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>73300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>53800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>9000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>28000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3797,123 +3930,129 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E59" s="3">
         <v>43100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15600</v>
       </c>
-      <c r="G59" s="3">
-        <v>38900</v>
-      </c>
       <c r="H59" s="3">
+        <v>63100</v>
+      </c>
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>64500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>58100</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E60" s="3">
         <v>82100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>254500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>198700</v>
       </c>
-      <c r="G60" s="3">
-        <v>195500</v>
-      </c>
       <c r="H60" s="3">
+        <v>93600</v>
+      </c>
+      <c r="I60" s="3">
         <v>254500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>241300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>169400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>74900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>81600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>111700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>95700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>128000</v>
-      </c>
-      <c r="P60" s="3">
-        <v>89000</v>
       </c>
       <c r="Q60" s="3">
         <v>89000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+      <c r="R60" s="3">
+        <v>89000</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
@@ -3921,68 +4060,71 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>848400</v>
+      </c>
+      <c r="E61" s="3">
         <v>800000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>573600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>536400</v>
       </c>
-      <c r="G61" s="3">
-        <v>547500</v>
-      </c>
       <c r="H61" s="3">
+        <v>680800</v>
+      </c>
+      <c r="I61" s="3">
         <v>473400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>483400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>487200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>368000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>368500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>284400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>259800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>92800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>87500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>96300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4001,76 +4143,82 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E62" s="3">
         <v>7400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28300</v>
       </c>
-      <c r="G62" s="3">
-        <v>32300</v>
-      </c>
       <c r="H62" s="3">
+        <v>900</v>
+      </c>
+      <c r="I62" s="3">
         <v>25700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>58800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>51500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
         <v>24600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4285,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4356,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,76 +4427,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>960500</v>
+      </c>
+      <c r="E66" s="3">
         <v>889400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>856800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>763300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>775300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>753800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>763200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>683000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>468400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>474100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>409700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>365900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>491600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>482400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>408900</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3">
         <v>24800</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4527,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4596,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4667,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4512,7 +4679,7 @@
         <v>30100</v>
       </c>
       <c r="E70" s="3">
-        <v>74300</v>
+        <v>30100</v>
       </c>
       <c r="F70" s="3">
         <v>74300</v>
@@ -4539,7 +4706,7 @@
         <v>74300</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -4571,8 +4738,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,76 +4809,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-862700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-897000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-919500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-936200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-944000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-706100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-638600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-563900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-542600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-528200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-506500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-475200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-414200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-380200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-305400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3">
         <v>7300</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4951,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5022,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,76 +5093,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>480000</v>
+      </c>
+      <c r="E76" s="3">
         <v>438300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>366800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>335500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>326500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>462300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>526000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>626800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>559700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>535900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>523200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>527900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>553500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>567200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>572800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3">
         <v>264200</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5235,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E81" s="3">
         <v>22500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-237900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-67500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-74800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-61000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-74800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-205700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-86500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7300</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,65 +5411,66 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-6500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-6700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>300</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
@@ -5282,8 +5480,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5551,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5622,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5693,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5764,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5835,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E89" s="3">
         <v>67000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34400</v>
       </c>
-      <c r="G89" s="3">
-        <v>32100</v>
-      </c>
       <c r="H89" s="3">
+        <v>27900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-7100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-25600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>9300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,62 +5935,63 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-3800</v>
       </c>
       <c r="F91" s="3">
         <v>-3800</v>
       </c>
       <c r="G91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-16600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
@@ -5784,8 +6004,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6075,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6146,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-125300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-26900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-36000</v>
-      </c>
       <c r="H94" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-105800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-114200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-228100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-96600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-125200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-91200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-99700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-73600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-87800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-104000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>48500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-190700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-287500</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6246,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6052,8 +6285,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6082,8 +6315,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6386,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6457,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,100 +6528,106 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E100" s="3">
         <v>12300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>78400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>48800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>25500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>63700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>298700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>63400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>110300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>103000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>46000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>37100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>354900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>24800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>20900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>243900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>289000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>600</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2700</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6404,8 +6652,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6422,72 +6670,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E102" s="3">
         <v>22700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>45500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-86900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-42100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>87500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-61600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-47200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>14600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-62900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>225200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>85300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>51000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>62500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>PGY</t>
   </si>
@@ -656,172 +656,176 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>317900</v>
+      </c>
+      <c r="E8" s="3">
         <v>334800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>350200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>326400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>290000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>279400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>257200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>250300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>245300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>218000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>211800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>195600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>186600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>192900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>204000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>352100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>154700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>136600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>183300</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
@@ -831,68 +835,71 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>177600</v>
+      </c>
+      <c r="E9" s="3">
         <v>190000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>191500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>167100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>158200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>149000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>145600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>144900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>134500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>128800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>120600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>125100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>124700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>129100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>197300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>50800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>81700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>99800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -902,68 +909,71 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>140400</v>
+      </c>
+      <c r="E10" s="3">
         <v>144800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>149600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>134900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>122900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>121200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>108300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>104700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>83600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>83000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>61600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>74900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>154800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>103900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>83500</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,68 +1013,69 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E12" s="3">
         <v>19100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>18200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>18500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>16700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>21100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>23600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>38600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>88700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>39400</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,32 +1159,35 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E14" s="3">
         <v>43700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>44500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>25800</v>
+      </c>
+      <c r="I14" s="3">
         <v>256300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>77800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1183,8 +1203,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1213,50 +1233,53 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E15" s="3">
         <v>1200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1600</v>
       </c>
-      <c r="G15" s="3">
-        <v>7700</v>
-      </c>
       <c r="H15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="I15" s="3">
         <v>1900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>237900</v>
+      </c>
+      <c r="E17" s="3">
         <v>255100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>270200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>269900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>242300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>247600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>234900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>245300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>237600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>207400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>211600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>205900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>211600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>219600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>268100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>512700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>156900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>121800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>201700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E18" s="3">
         <v>79700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>80000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>56500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>47700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>31800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-25000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-64100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-160600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,139 +1510,143 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E20" s="3">
         <v>14000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>27400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>34900</v>
       </c>
-      <c r="G20" s="3">
-        <v>47700</v>
-      </c>
       <c r="H20" s="3">
+        <v>21900</v>
+      </c>
+      <c r="I20" s="3">
         <v>16000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>30300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>73200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>34300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>47300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>67000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-34700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-32800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>7400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E21" s="3">
         <v>67000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>54400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23100</v>
       </c>
-      <c r="G21" s="3">
-        <v>7700</v>
-      </c>
       <c r="H21" s="3">
+        <v>27300</v>
+      </c>
+      <c r="I21" s="3">
         <v>17700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-61100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-20300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-41900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-22700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-88400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-58000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-152900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-36900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,8 +1656,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1660,8 +1700,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1690,139 +1730,145 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E23" s="3">
         <v>22100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21500</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>-240500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-85800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-68200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-47100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-27100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-92000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-61400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-60900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-154000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-37200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7300</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-11500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-9200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7800</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E26" s="3">
         <v>29000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-257100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-74200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-82700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-20000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-45900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-32100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-98600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-67000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-173600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-45000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7300</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E27" s="3">
         <v>33000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>15600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-237900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-67500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-74800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-61000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-74800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-205700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-86500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>7300</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,150 +2396,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-14000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-27400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-34900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-47700</v>
-      </c>
       <c r="H32" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="I32" s="3">
         <v>-16000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-30300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-73200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-34300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-47300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-67000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>34700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>32800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-7400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E33" s="3">
         <v>34300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-237900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-67500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-74800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-61000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-74800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-205700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-86500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>7300</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E35" s="3">
         <v>34300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-237900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-67500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-74800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-61000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-74800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-205700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-86500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>7300</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,121 +2829,125 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>317800</v>
+      </c>
+      <c r="E41" s="3">
         <v>235300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>218300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>183000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>186800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>187900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>147100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>233600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>274500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>186500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>252600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>304000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>289400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>309800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>327900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>415000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3">
         <v>700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>941400</v>
+      </c>
+      <c r="E42" s="3">
         <v>945300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>887700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>778400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3300</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2885,67 +2975,70 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>180100</v>
+      </c>
+      <c r="E43" s="3">
         <v>166300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>155000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>118500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>107500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>127100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>99900</v>
-      </c>
-      <c r="K43" s="3">
-        <v>87400</v>
       </c>
       <c r="L43" s="3">
         <v>87400</v>
       </c>
       <c r="M43" s="3">
+        <v>87400</v>
+      </c>
+      <c r="N43" s="3">
         <v>71500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>68000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>58500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>60200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>39200</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2997,8 +3093,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3027,8 +3123,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3056,251 +3155,260 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>49800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>56700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17900</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3">
         <v>800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1501500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1406800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1307500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>362500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>355600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1139600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>298500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>361200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>399100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>303400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>378000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>421400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>399200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>419800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>439100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>472100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3">
         <v>1400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E47" s="3">
         <v>13500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>868000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>762400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>937900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>936400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>919800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>740700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>692000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>614900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>530800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>527600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>499900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>433000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3">
         <v>287500</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>60400</v>
+      </c>
+      <c r="E48" s="3">
         <v>60800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>64600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>71500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>92300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>96400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>97300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>95300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>94800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>93300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>92700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>94600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>66800</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
@@ -3311,50 +3419,53 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E49" s="3">
         <v>30600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>33400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>34600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>35900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3370,8 +3481,8 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,43 +3641,46 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E52" s="3">
         <v>34200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>36500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>36200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>18000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>4900</v>
       </c>
       <c r="O52" s="3">
         <v>4900</v>
@@ -3569,14 +3689,14 @@
         <v>4900</v>
       </c>
       <c r="Q52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="R52" s="3">
         <v>16000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9900</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,79 +3789,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1648600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1545900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1455400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1399000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1278400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1291100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1370800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1453000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1483200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1208400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1220200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1187100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1082400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1045100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1049600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>981700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3">
         <v>288900</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,67 +3921,68 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>1300</v>
       </c>
       <c r="M57" s="3">
         <v>1300</v>
       </c>
       <c r="N57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O57" s="3">
         <v>3800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2900</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -3862,67 +3993,70 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>114700</v>
+      </c>
+      <c r="E58" s="3">
         <v>10100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>190100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>142400</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>213700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>195400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>127500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>44600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>50400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>73300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>53800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>61800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>28000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3933,129 +4067,135 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E59" s="3">
         <v>53000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>43100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>63100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>64500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>58100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3">
         <v>200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>205500</v>
+      </c>
+      <c r="E60" s="3">
         <v>107300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>82100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>254500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>198700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>254500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>241300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>169400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>74900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>81600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>111700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>95700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>128000</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>89000</v>
       </c>
       <c r="R60" s="3">
         <v>89000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>89000</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -4063,71 +4203,74 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>813300</v>
+      </c>
+      <c r="E61" s="3">
         <v>848400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>800000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>573600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>536400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>680800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>473400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>483400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>487200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>368000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>368500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>284400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>259800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>92800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>87500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>96300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4146,79 +4289,85 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>58800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>51500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3">
         <v>24600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,79 +4585,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1019400</v>
+      </c>
+      <c r="E66" s="3">
         <v>960500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>889400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>856800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>763300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>775300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>753800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>763200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>683000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>468400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>474100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>409700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>365900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>491600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>482400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>408900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3">
         <v>24800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4682,7 +4850,7 @@
         <v>30100</v>
       </c>
       <c r="F70" s="3">
-        <v>74300</v>
+        <v>30100</v>
       </c>
       <c r="G70" s="3">
         <v>74300</v>
@@ -4709,7 +4877,7 @@
         <v>74300</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
+        <v>74300</v>
       </c>
       <c r="P70" s="3">
         <v>0</v>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,79 +4983,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-838000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-862700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-897000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-919500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-936200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-944000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-706100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-638600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-563900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-542600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-528200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-506500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-475200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-414200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-380200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-305400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3">
         <v>7300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,79 +5279,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>529300</v>
+      </c>
+      <c r="E76" s="3">
         <v>480000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>438300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>366800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>335500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>326500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>462300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>526000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>626800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>559700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>535900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>523200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>527900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>553500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>567200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>572800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3">
         <v>264200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E81" s="3">
         <v>34300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-237900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-67500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-74800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-61000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-34000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-74800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-205700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-86500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>7300</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,68 +5610,69 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>500</v>
       </c>
-      <c r="F83" s="3">
-        <v>-6500</v>
-      </c>
       <c r="G83" s="3">
-        <v>6300</v>
+        <v>-900</v>
       </c>
       <c r="H83" s="3">
+        <v>700</v>
+      </c>
+      <c r="I83" s="3">
         <v>15300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-6700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E89" s="3">
         <v>79800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>67000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>34400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>27900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-23700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-25600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,65 +6156,66 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-3800</v>
       </c>
       <c r="G91" s="3">
         <v>-3800</v>
       </c>
       <c r="H91" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,79 +6376,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-125300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-105800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-228100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-96600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-125200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-91200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-99700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-73600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-87800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-104000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>48500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-190700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-287500</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6288,8 +6522,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,106 +6774,112 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E100" s="3">
         <v>42700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>78400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>48800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>25500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>63700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>298700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>63400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>110300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>103000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>46000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>37100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>354900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>24800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>20900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>243900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>289000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2700</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6655,8 +6904,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6673,75 +6922,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E102" s="3">
         <v>23600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>45500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-86900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-42100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>87500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-61600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-47200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-29700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-62900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>225200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>85300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>51000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>62500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
